--- a/data/trans_bre/KIDM_C_3_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_C_3_R-Edad-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -612,42 +612,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,13</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,68</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-7,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,26; 6,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,55; 12,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,04; 4,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,42; 5,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-40,55; 289,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,85; 124,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-51,71; 60,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,5; 499,37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>12-15</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -712,42 +712,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1,15</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-10,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>405,3%</t>
         </is>
       </c>
     </row>
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,5; 4,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,43; 7,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,76; 4,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,46; 7,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-47,24; 187,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-35,05; 83,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-49,36; 53,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,56; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8-11</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -812,42 +812,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,13</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,46</t>
+          <t>3,52</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>1,84</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>-7,5%</t>
+          <t>-9,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -860,262 +860,60 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 6,42</t>
+          <t>-1,46; 4,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 12,72</t>
+          <t>-0,94; 8,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 3,75</t>
+          <t>-4,86; 2,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 5,82</t>
+          <t>-0,88; 4,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,64; 305,61</t>
+          <t>-28,08; 142,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 143,72</t>
+          <t>-7,3; 85,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-53,79; 57,92</t>
+          <t>-42,29; 34,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-81,73; 471,09</t>
+          <t>-38,01; 569,29</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,9</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-10,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>405,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,52; 4,18</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,78; 7,06</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-7,23; 4,38</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,21; 6,36</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-50,41; 170,15</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-29,44; 87,98</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-52,8; 54,68</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-64,03; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3,52</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>30,59%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>30,1%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-9,24%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95,86%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,23; 4,05</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,82; 7,88</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-4,68; 2,94</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-0,94; 5,1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-25,9; 139,95</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-7,65; 77,65</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-38,98; 36,91</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-36,27; 561,79</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="6">
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_bre/KIDM_C_3_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_C_3_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 6,52</t>
+          <t>-2,06; 6,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 12,04</t>
+          <t>-1,31; 12,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 4,12</t>
+          <t>-5,57; 4,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 5,8</t>
+          <t>-5,03; 5,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-40,55; 289,2</t>
+          <t>-44,97; 300,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 124,97</t>
+          <t>-10,23; 139,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,71; 60,56</t>
+          <t>-46,91; 69,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-80,5; 499,37</t>
+          <t>-86,94; 444,92</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 4,67</t>
+          <t>-2,82; 4,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 7,11</t>
+          <t>-3,52; 7,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 4,42</t>
+          <t>-6,44; 4,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 7,18</t>
+          <t>0,28; 6,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,24; 187,68</t>
+          <t>-49,96; 185,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 83,0</t>
+          <t>-25,27; 94,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,36; 53,28</t>
+          <t>-48,38; 60,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,56; —</t>
+          <t>-43,68; —</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 4,06</t>
+          <t>-1,51; 4,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 8,2</t>
+          <t>-0,73; 7,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 2,84</t>
+          <t>-4,68; 2,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 4,91</t>
+          <t>-0,71; 5,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,08; 142,54</t>
+          <t>-30,37; 149,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 85,02</t>
+          <t>-5,5; 83,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-42,29; 34,79</t>
+          <t>-39,86; 34,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 569,29</t>
+          <t>-31,76; 617,21</t>
         </is>
       </c>
     </row>
